--- a/Listing/DND05S.xlsx
+++ b/Listing/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="658">
   <si>
     <t/>
   </si>
@@ -61,6 +61,15 @@
     <t>PT,(E-1B)</t>
   </si>
   <si>
+    <t>20073805</t>
+  </si>
+  <si>
+    <t>SOKLN RED/MG&amp;B1.44KG</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>20123338</t>
   </si>
   <si>
@@ -82,10 +91,34 @@
     <t>SOKLIN CAIR VIO 1.6L</t>
   </si>
   <si>
-    <t>20128710</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ360</t>
+    <t>20067585</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ RED SB 700</t>
+  </si>
+  <si>
+    <t>20054747</t>
+  </si>
+  <si>
+    <t>SO KLIN VL/BLSOM 700</t>
+  </si>
+  <si>
+    <t>20046548</t>
+  </si>
+  <si>
+    <t>SOKLIN SOFT CAIR 700</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20137791</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ HJB 700</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
   <si>
     <t>20131373</t>
@@ -94,33 +127,6 @@
     <t>GENTLE GEN FR.PE 360</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20131374</t>
-  </si>
-  <si>
-    <t>GENTLE GEN PRS.G 360</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20134544</t>
-  </si>
-  <si>
-    <t>RINSO DET JPN.PCH360</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20134545</t>
-  </si>
-  <si>
-    <t>RINSO DET KRN.STR360</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -238,28 +244,31 @@
     <t>SOKLN LIQ KOREAN 510</t>
   </si>
   <si>
-    <t>20067585</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ RED SB 700</t>
-  </si>
-  <si>
-    <t>20054747</t>
-  </si>
-  <si>
-    <t>SO KLIN VL/BLSOM 700</t>
-  </si>
-  <si>
-    <t>20046548</t>
-  </si>
-  <si>
-    <t>SOKLIN SOFT CAIR 700</t>
-  </si>
-  <si>
-    <t>20137791</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ HJB 700</t>
+    <t>20131730</t>
+  </si>
+  <si>
+    <t>SYANG LIQ R/ROSE 700</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20132442</t>
+  </si>
+  <si>
+    <t>SYANG LIQ ORIGNAL700</t>
+  </si>
+  <si>
+    <t>20135849</t>
+  </si>
+  <si>
+    <t>LARIST SMR.BRZ 700ML</t>
+  </si>
+  <si>
+    <t>20139955</t>
+  </si>
+  <si>
+    <t>BU KRM JNHAE CB700ML</t>
   </si>
   <si>
     <t>20037446</t>
@@ -277,6 +286,12 @@
     <t>PT,(E-1.5B)</t>
   </si>
   <si>
+    <t>20141203</t>
+  </si>
+  <si>
+    <t>RINSO RYL GOLD 700G</t>
+  </si>
+  <si>
     <t>20140001</t>
   </si>
   <si>
@@ -316,25 +331,25 @@
     <t>RT</t>
   </si>
   <si>
-    <t>20131730</t>
-  </si>
-  <si>
-    <t>SYANG LIQ R/ROSE 700</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20132442</t>
-  </si>
-  <si>
-    <t>SYANG LIQ ORIGNAL700</t>
-  </si>
-  <si>
-    <t>20135849</t>
-  </si>
-  <si>
-    <t>LARIST SMR.BRZ 700ML</t>
+    <t>20141373</t>
+  </si>
+  <si>
+    <t>RINSO PW.CLN BTL 650</t>
+  </si>
+  <si>
+    <t>TG</t>
+  </si>
+  <si>
+    <t>20141369</t>
+  </si>
+  <si>
+    <t>RINSO P.BRZE BTL 650</t>
+  </si>
+  <si>
+    <t>20141372</t>
+  </si>
+  <si>
+    <t>GENTLE GEN LILAC 700</t>
   </si>
   <si>
     <t>20135245</t>
@@ -379,10 +394,10 @@
     <t>GENTLE GEN A/KRGT700</t>
   </si>
   <si>
-    <t>20139955</t>
-  </si>
-  <si>
-    <t>BU KRM JNHAE CB700ML</t>
+    <t>20141371</t>
+  </si>
+  <si>
+    <t>GNTLE GEN CMLLIA 700</t>
   </si>
   <si>
     <t>20099414</t>
@@ -397,10 +412,262 @@
     <t>SO/KLN SOFT P/RS1.44</t>
   </si>
   <si>
-    <t>20073805</t>
-  </si>
-  <si>
-    <t>SOKLN RED/MG&amp;B1.44KG</t>
+    <t>20140806</t>
+  </si>
+  <si>
+    <t>SO KLN EDP D.LS 144</t>
+  </si>
+  <si>
+    <t>20140804</t>
+  </si>
+  <si>
+    <t>SO KLN EDP BLNC 1.44</t>
+  </si>
+  <si>
+    <t>20052321</t>
+  </si>
+  <si>
+    <t>DAIA+SOFT PINK 1.5KG</t>
+  </si>
+  <si>
+    <t>20091352</t>
+  </si>
+  <si>
+    <t>DAIA+SOFT VIOLET 1.5</t>
+  </si>
+  <si>
+    <t>20030446</t>
+  </si>
+  <si>
+    <t>DAIA PUTIH 1.5KG</t>
+  </si>
+  <si>
+    <t>20121050</t>
+  </si>
+  <si>
+    <t>DAIA HIJAB C&amp;F 1.5G</t>
+  </si>
+  <si>
+    <t>10014547</t>
+  </si>
+  <si>
+    <t>DAIA DTRG.BBK BGA1.5</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20053796</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTG PRPL 720</t>
+  </si>
+  <si>
+    <t>20073499</t>
+  </si>
+  <si>
+    <t>SO KLN MGNL&amp;BRY 720G</t>
+  </si>
+  <si>
+    <t>20012188</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTR ROSY 720</t>
+  </si>
+  <si>
+    <t>20119238</t>
+  </si>
+  <si>
+    <t>TOTAL DET.PERFUME750</t>
+  </si>
+  <si>
+    <t>20061748</t>
+  </si>
+  <si>
+    <t>DAIA DET+SFT VLT 800</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20036047</t>
+  </si>
+  <si>
+    <t>DAIA DET+SOFT  800G</t>
+  </si>
+  <si>
+    <t>20012007</t>
+  </si>
+  <si>
+    <t>DAIA DET.BBK PTH 800</t>
+  </si>
+  <si>
+    <t>10005245</t>
+  </si>
+  <si>
+    <t>DAIA BBK FLORAL 800G</t>
+  </si>
+  <si>
+    <t>20074992</t>
+  </si>
+  <si>
+    <t>BUKRIM OXY/K VIOL700</t>
+  </si>
+  <si>
+    <t>20067586</t>
+  </si>
+  <si>
+    <t>SOKLIN LIQ.BM TOP700</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20054610</t>
+  </si>
+  <si>
+    <t>RINSO LIQ FRONT 1.45</t>
+  </si>
+  <si>
+    <t>10030924</t>
+  </si>
+  <si>
+    <t>SOKLIN MTC F/LD 900G</t>
+  </si>
+  <si>
+    <t>20131792</t>
+  </si>
+  <si>
+    <t>BOOM DET.BBK LVND770</t>
+  </si>
+  <si>
+    <t>20123022</t>
+  </si>
+  <si>
+    <t>SAYANG PWDR ROSE 770</t>
+  </si>
+  <si>
+    <t>20131516</t>
+  </si>
+  <si>
+    <t>LARIST DET.FRS BT450</t>
+  </si>
+  <si>
+    <t>20081448</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT H.SM 650</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20081449</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT P.DW 650</t>
+  </si>
+  <si>
+    <t>20113101</t>
+  </si>
+  <si>
+    <t>ROYALE SWT FLORL 680</t>
+  </si>
+  <si>
+    <t>20104951</t>
+  </si>
+  <si>
+    <t>ROYALE HJB BLCK.V650</t>
+  </si>
+  <si>
+    <t>20091457</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT BS 650</t>
+  </si>
+  <si>
+    <t>20128706</t>
+  </si>
+  <si>
+    <t>ROYALE LNVDR VNL 680</t>
+  </si>
+  <si>
+    <t>20113093</t>
+  </si>
+  <si>
+    <t>ROYALE SUNNY DAY 680</t>
+  </si>
+  <si>
+    <t>20098312</t>
+  </si>
+  <si>
+    <t>ROYALE PINK STN 650</t>
+  </si>
+  <si>
+    <t>20126740</t>
+  </si>
+  <si>
+    <t>MOLTO FRSH.CSBLCA650</t>
+  </si>
+  <si>
+    <t>20094735</t>
+  </si>
+  <si>
+    <t>DOWNY SUNRISE 950</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20094733</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 850</t>
+  </si>
+  <si>
+    <t>20140221</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 950ML</t>
+  </si>
+  <si>
+    <t>20074226</t>
+  </si>
+  <si>
+    <t>DOWNY SUN.FRSH 600</t>
+  </si>
+  <si>
+    <t>20080360</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 600ML</t>
+  </si>
+  <si>
+    <t>20080361</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 600ML</t>
+  </si>
+  <si>
+    <t>20139145</t>
+  </si>
+  <si>
+    <t>DOWNY MLKY TOUCH 500</t>
+  </si>
+  <si>
+    <t>20141324</t>
+  </si>
+  <si>
+    <t>DOWNY SUNSHINE 500ML</t>
+  </si>
+  <si>
+    <t>20141323</t>
+  </si>
+  <si>
+    <t>DOWNY MIDNIGHT 500ML</t>
   </si>
   <si>
     <t>20140003</t>
@@ -409,253 +676,19 @@
     <t>RNSO PWD ROSE.F 1.44</t>
   </si>
   <si>
-    <t>20052321</t>
-  </si>
-  <si>
-    <t>DAIA+SOFT PINK 1.5KG</t>
-  </si>
-  <si>
-    <t>20091352</t>
-  </si>
-  <si>
-    <t>DAIA+SOFT VIOLET 1.5</t>
-  </si>
-  <si>
-    <t>20030446</t>
-  </si>
-  <si>
-    <t>DAIA PUTIH 1.5KG</t>
-  </si>
-  <si>
-    <t>20121050</t>
-  </si>
-  <si>
-    <t>DAIA HIJAB C&amp;F 1.5G</t>
-  </si>
-  <si>
-    <t>10014547</t>
-  </si>
-  <si>
-    <t>DAIA DTRG.BBK BGA1.5</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20131792</t>
-  </si>
-  <si>
-    <t>BOOM DET.BBK LVND770</t>
-  </si>
-  <si>
-    <t>20131790</t>
-  </si>
-  <si>
-    <t>BOOM DET.BBK ROSE770</t>
-  </si>
-  <si>
-    <t>20123022</t>
-  </si>
-  <si>
-    <t>SAYANG PWDR ROSE 770</t>
-  </si>
-  <si>
-    <t>20061748</t>
-  </si>
-  <si>
-    <t>DAIA DET+SFT VLT 800</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20036047</t>
-  </si>
-  <si>
-    <t>DAIA DET+SOFT  800G</t>
-  </si>
-  <si>
-    <t>20012007</t>
-  </si>
-  <si>
-    <t>DAIA DET.BBK PTH 800</t>
-  </si>
-  <si>
-    <t>10005245</t>
-  </si>
-  <si>
-    <t>DAIA BBK FLORAL 800G</t>
-  </si>
-  <si>
-    <t>20074992</t>
-  </si>
-  <si>
-    <t>BUKRIM OXY/K VIOL700</t>
-  </si>
-  <si>
-    <t>20125692</t>
-  </si>
-  <si>
-    <t>IDM DET MATIC 700ML</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20067586</t>
-  </si>
-  <si>
-    <t>SOKLIN LIQ.BM TOP700</t>
-  </si>
-  <si>
-    <t>20131366</t>
-  </si>
-  <si>
-    <t>RINSO LIQ.MTC TOP700</t>
-  </si>
-  <si>
-    <t>20054610</t>
-  </si>
-  <si>
-    <t>RINSO LIQ FRONT 1.45</t>
-  </si>
-  <si>
-    <t>20086327</t>
-  </si>
-  <si>
-    <t>RINSO MTC FRN/L 900G</t>
-  </si>
-  <si>
-    <t>10030924</t>
-  </si>
-  <si>
-    <t>SOKLIN MTC F/LD 900G</t>
-  </si>
-  <si>
-    <t>20119238</t>
-  </si>
-  <si>
-    <t>TOTAL DET.PERFUME750</t>
-  </si>
-  <si>
-    <t>20081448</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT H.SM 650</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20081449</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT P.DW 650</t>
-  </si>
-  <si>
-    <t>20113101</t>
-  </si>
-  <si>
-    <t>ROYALE SWT FLORL 680</t>
-  </si>
-  <si>
-    <t>20104951</t>
-  </si>
-  <si>
-    <t>ROYALE HJB BLCK.V650</t>
-  </si>
-  <si>
-    <t>20091457</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT BS 650</t>
-  </si>
-  <si>
-    <t>20128706</t>
-  </si>
-  <si>
-    <t>ROYALE LNVDR VNL 680</t>
-  </si>
-  <si>
-    <t>20113093</t>
-  </si>
-  <si>
-    <t>ROYALE SUNNY DAY 680</t>
-  </si>
-  <si>
-    <t>20098312</t>
-  </si>
-  <si>
-    <t>ROYALE PINK STN 650</t>
-  </si>
-  <si>
-    <t>20126740</t>
-  </si>
-  <si>
-    <t>MOLTO FRSH.CSBLCA650</t>
-  </si>
-  <si>
-    <t>20094735</t>
-  </si>
-  <si>
-    <t>DOWNY SUNRISE 950</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20094733</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 850</t>
-  </si>
-  <si>
-    <t>20140221</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 950ML</t>
-  </si>
-  <si>
-    <t>20074226</t>
-  </si>
-  <si>
-    <t>DOWNY SUN.FRSH 600</t>
-  </si>
-  <si>
-    <t>20080360</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 600ML</t>
-  </si>
-  <si>
-    <t>20080361</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 600ML</t>
-  </si>
-  <si>
-    <t>20087479</t>
-  </si>
-  <si>
-    <t>DOWNY FLO.PINK 600ML</t>
-  </si>
-  <si>
-    <t>20139145</t>
-  </si>
-  <si>
-    <t>DOWNY MLKY TOUCH 500</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20093521</t>
+  </si>
+  <si>
+    <t>RINSO+MOLTO ESC1440G</t>
   </si>
   <si>
     <t>20139609</t>
   </si>
   <si>
-    <t>RNSO JPN PEAC 1.44KG</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>RNSO JPN PEAC 1440G</t>
   </si>
   <si>
     <t>20140002</t>
@@ -670,33 +703,15 @@
     <t>ATCK JAZ1 S/CNTA 1.5</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>20064414</t>
   </si>
   <si>
     <t>ATTACK JAZ1 P/SGR1.5</t>
   </si>
   <si>
-    <t>20053796</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTG PRPL 720</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20073499</t>
-  </si>
-  <si>
-    <t>SO KLN MGNL&amp;BRY 720G</t>
-  </si>
-  <si>
-    <t>20012188</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTR ROSY 720</t>
-  </si>
-  <si>
     <t>20130527</t>
   </si>
   <si>
@@ -709,21 +724,21 @@
     <t>JAZ 1 PRPL BLS 1.4KG</t>
   </si>
   <si>
+    <t>20071827</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 700</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>20085113</t>
   </si>
   <si>
     <t>RNSO+ML PWD PRFM 700</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20071827</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 700</t>
-  </si>
-  <si>
     <t>20123256</t>
   </si>
   <si>
@@ -742,45 +757,39 @@
     <t>ATTACK JAZ1 S/CNT800</t>
   </si>
   <si>
+    <t>20105968</t>
+  </si>
+  <si>
+    <t>RNSO PWD JPN PC 700G</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20113183</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD ROSE 380</t>
+  </si>
+  <si>
+    <t>20121372</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 380</t>
+  </si>
+  <si>
     <t>20128719</t>
   </si>
   <si>
     <t>SOKLIN LVD&amp;LILY 425G</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20131220</t>
-  </si>
-  <si>
-    <t>SO KLN PNY&amp;ROSE 400G</t>
-  </si>
-  <si>
     <t>20042466</t>
   </si>
   <si>
     <t>DAIA DET+SOFT 470G</t>
   </si>
   <si>
-    <t>20113183</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD ROSE 380</t>
-  </si>
-  <si>
-    <t>20121372</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 380</t>
-  </si>
-  <si>
-    <t>20131516</t>
-  </si>
-  <si>
-    <t>LARIST DET.FRS BT450</t>
-  </si>
-  <si>
     <t>20139595</t>
   </si>
   <si>
@@ -982,18 +991,18 @@
     <t>RT,(E-3.5B)</t>
   </si>
   <si>
+    <t>20082581</t>
+  </si>
+  <si>
+    <t>VANISH CAIR WHT 425</t>
+  </si>
+  <si>
     <t>20052662</t>
   </si>
   <si>
     <t>VANISH CAIR PCH 425</t>
   </si>
   <si>
-    <t>20082581</t>
-  </si>
-  <si>
-    <t>VANISH CAIR WHT 425</t>
-  </si>
-  <si>
     <t>20089665</t>
   </si>
   <si>
@@ -1015,7 +1024,7 @@
     <t>10014263</t>
   </si>
   <si>
-    <t>WIPOL KARBOL CMR 730</t>
+    <t>WIPOL KARBOL CMR 720</t>
   </si>
   <si>
     <t>23</t>
@@ -1024,13 +1033,13 @@
     <t>20001645</t>
   </si>
   <si>
-    <t>WIPOL KARBOL LMN 730</t>
+    <t>WIPOL KARBOL LMN 720</t>
   </si>
   <si>
     <t>20090066</t>
   </si>
   <si>
-    <t>WIPOL SRH + JRK 730</t>
+    <t>WIPOL SRH + JRK 720</t>
   </si>
   <si>
     <t>20122478</t>
@@ -1123,82 +1132,172 @@
     <t>IDM KRBL SRH CTR 650</t>
   </si>
   <si>
+    <t>20128125</t>
+  </si>
+  <si>
+    <t>IDM PURPOSE CLN 375</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20027963</t>
+  </si>
+  <si>
+    <t>IDM PMBERSH KACA 400</t>
+  </si>
+  <si>
+    <t>10003706</t>
+  </si>
+  <si>
+    <t>MR.MUSCLE ORGNL 400</t>
+  </si>
+  <si>
+    <t>10012548</t>
+  </si>
+  <si>
+    <t>SOKLIN RLX/LAV RF770</t>
+  </si>
+  <si>
+    <t>10003646</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L APPLE770</t>
+  </si>
+  <si>
+    <t>10003645</t>
+  </si>
+  <si>
+    <t>SO KLIN P/L LMN 780</t>
+  </si>
+  <si>
+    <t>20101095</t>
+  </si>
+  <si>
+    <t>SO KLN LNT SEREH 770</t>
+  </si>
+  <si>
+    <t>20131223</t>
+  </si>
+  <si>
+    <t>SO KLN LNT CT.GRD700</t>
+  </si>
+  <si>
+    <t>20131788</t>
+  </si>
+  <si>
+    <t>MAMA LMN JR.NPS 950</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20092331</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ JR.NP650</t>
+  </si>
+  <si>
+    <t>20123812</t>
+  </si>
+  <si>
+    <t>EKONOMI LQ.SEREH 650</t>
+  </si>
+  <si>
+    <t>20107240</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ.SW&amp;JR650</t>
+  </si>
+  <si>
+    <t>20136124</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ N&amp;JN 675G</t>
+  </si>
+  <si>
+    <t>20129722</t>
+  </si>
+  <si>
+    <t>BUKRIM LIQ.JRK NP550</t>
+  </si>
+  <si>
+    <t>20138518</t>
+  </si>
+  <si>
+    <t>KILAU NIPIS 630ML</t>
+  </si>
+  <si>
+    <t>20034450</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 690</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>10004067</t>
+  </si>
+  <si>
+    <t>MAMA/L PCH LEMON 690</t>
+  </si>
+  <si>
+    <t>20099424</t>
+  </si>
+  <si>
+    <t>MAMA LIME CHARCO 690</t>
+  </si>
+  <si>
+    <t>20052031</t>
+  </si>
+  <si>
+    <t>MAMA LIME GRN TEA690</t>
+  </si>
+  <si>
+    <t>10004068</t>
+  </si>
+  <si>
+    <t>MAMA LIME POUCH 690</t>
+  </si>
+  <si>
+    <t>20134303</t>
+  </si>
+  <si>
+    <t>MAMA/L REF YUZU 690</t>
+  </si>
+  <si>
+    <t>20137792</t>
+  </si>
+  <si>
+    <t>MAMA LIME GREEN 690</t>
+  </si>
+  <si>
+    <t>20034449</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 430</t>
+  </si>
+  <si>
+    <t>20090067</t>
+  </si>
+  <si>
+    <t>SNLGHT MINT A.BAU600</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20086172</t>
+  </si>
+  <si>
+    <t>SNLIGHT MND.ORGE 600</t>
+  </si>
+  <si>
     <t>20112492</t>
   </si>
   <si>
-    <t>SUNLIGHT LIME 430G</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20034449</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 430</t>
-  </si>
-  <si>
-    <t>10012548</t>
-  </si>
-  <si>
-    <t>SOKLIN RLX/LAV RF770</t>
-  </si>
-  <si>
-    <t>10003646</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L APPLE770</t>
-  </si>
-  <si>
-    <t>10003645</t>
-  </si>
-  <si>
-    <t>SO KLIN P/L LMN 780</t>
-  </si>
-  <si>
-    <t>20101095</t>
-  </si>
-  <si>
-    <t>SO KLN LNT SEREH 770</t>
-  </si>
-  <si>
-    <t>20131223</t>
-  </si>
-  <si>
-    <t>SO KLN LNT CT.GRD700</t>
-  </si>
-  <si>
-    <t>20131788</t>
-  </si>
-  <si>
-    <t>MAMA LMN JR.NPS 950</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20092331</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ JR.NP650</t>
-  </si>
-  <si>
-    <t>20123812</t>
-  </si>
-  <si>
-    <t>EKONOMI LQ.SEREH 650</t>
-  </si>
-  <si>
-    <t>20107240</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ.SW&amp;JR650</t>
-  </si>
-  <si>
-    <t>20136124</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ N&amp;JN 675G</t>
+    <t>SUNLIGHT JRK NPS400G</t>
   </si>
   <si>
     <t>20128374</t>
@@ -1213,55 +1312,37 @@
     <t>LFEBUOY REF LEMON650</t>
   </si>
   <si>
-    <t>20034450</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 690</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>10004067</t>
-  </si>
-  <si>
-    <t>MAMA/L PCH LEMON 690</t>
-  </si>
-  <si>
-    <t>20099424</t>
-  </si>
-  <si>
-    <t>MAMA LIME CHARCO 690</t>
-  </si>
-  <si>
-    <t>20052031</t>
-  </si>
-  <si>
-    <t>MAMA LIME GRN TEA690</t>
-  </si>
-  <si>
-    <t>10004068</t>
-  </si>
-  <si>
-    <t>MAMA LIME POUCH 690</t>
-  </si>
-  <si>
-    <t>20134303</t>
-  </si>
-  <si>
-    <t>MAMA/L REF YUZU 690</t>
-  </si>
-  <si>
-    <t>20137792</t>
-  </si>
-  <si>
-    <t>MAMA LIME GREEN 690</t>
-  </si>
-  <si>
-    <t>20129722</t>
-  </si>
-  <si>
-    <t>BUKRIM LIQ.JRK NP550</t>
+    <t>20073425</t>
+  </si>
+  <si>
+    <t>IDM P.PRNG JRK.N 650</t>
+  </si>
+  <si>
+    <t>20141204</t>
+  </si>
+  <si>
+    <t>IDM P.PRG JR.NPS 950</t>
+  </si>
+  <si>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20139728</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 870G</t>
+  </si>
+  <si>
+    <t>10005482</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 660</t>
   </si>
   <si>
     <t>20135144</t>
@@ -1270,78 +1351,6 @@
     <t>SNLGHT BIO NATURE600</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20090067</t>
-  </si>
-  <si>
-    <t>SNLGHT MINT A.BAU600</t>
-  </si>
-  <si>
-    <t>20086172</t>
-  </si>
-  <si>
-    <t>SNLIGHT MND.ORGE 600</t>
-  </si>
-  <si>
-    <t>20073425</t>
-  </si>
-  <si>
-    <t>IDM P.PRNG JRK.N 650</t>
-  </si>
-  <si>
-    <t>20132940</t>
-  </si>
-  <si>
-    <t>IDM P.PRNG LEMON 650</t>
-  </si>
-  <si>
-    <t>20138518</t>
-  </si>
-  <si>
-    <t>KILAU NIPIS 630ML</t>
-  </si>
-  <si>
-    <t>20128125</t>
-  </si>
-  <si>
-    <t>IDM PURPOSE CLN 375</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20027963</t>
-  </si>
-  <si>
-    <t>IDM PMBERSH KACA 400</t>
-  </si>
-  <si>
-    <t>10003706</t>
-  </si>
-  <si>
-    <t>MR.MUSCLE ORGNL 400</t>
-  </si>
-  <si>
-    <t>20139728</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 870G</t>
-  </si>
-  <si>
-    <t>20112491</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 910</t>
-  </si>
-  <si>
-    <t>10005482</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 660</t>
-  </si>
-  <si>
     <t>10013205</t>
   </si>
   <si>
@@ -1402,7 +1411,7 @@
     <t>10004032</t>
   </si>
   <si>
-    <t>VIXAL KUAT HARUM 750</t>
+    <t>VIXAL KUAT HARUM 720</t>
   </si>
   <si>
     <t>31</t>
@@ -1411,13 +1420,13 @@
     <t>10004034</t>
   </si>
   <si>
-    <t>VIXAL KMR MD KUAT750</t>
+    <t>VIXAL KMR MD KUAT720</t>
   </si>
   <si>
     <t>10003359</t>
   </si>
   <si>
-    <t>WIPOL P.LNT BTL 730</t>
+    <t>WIPOL CEMARA BTL 730</t>
   </si>
   <si>
     <t>10000955</t>
@@ -1528,12 +1537,6 @@
     <t>SOFFELL A.NYMK K/J60</t>
   </si>
   <si>
-    <t>10035178</t>
-  </si>
-  <si>
-    <t>DORA RACUN TIKUS 100</t>
-  </si>
-  <si>
     <t>10037280</t>
   </si>
   <si>
@@ -1927,7 +1930,7 @@
     <t>20124418</t>
   </si>
   <si>
-    <t>VAPE SWEET PWDR 240</t>
+    <t>VAPE SWEET PWDR 200</t>
   </si>
   <si>
     <t>20139446</t>
@@ -2495,13 +2498,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2518,18 +2521,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -2538,7 +2541,7 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -2546,10 +2549,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -2558,7 +2561,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -2566,10 +2569,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -2578,7 +2581,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -2598,7 +2601,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -2606,10 +2609,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -2618,18 +2621,18 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -2638,27 +2641,27 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -2678,7 +2681,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -2698,7 +2701,7 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -2718,7 +2721,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -2738,7 +2741,7 @@
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -2758,7 +2761,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -2778,18 +2781,18 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2798,10 +2801,10 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2818,30 +2821,30 @@
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2858,10 +2861,10 @@
         <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2878,10 +2881,10 @@
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2898,10 +2901,10 @@
         <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2918,10 +2921,10 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2938,10 +2941,10 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2958,7 +2961,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2978,7 +2981,7 @@
         <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2998,7 +3001,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -3015,10 +3018,10 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -3035,93 +3038,93 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3135,70 +3138,70 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -3206,19 +3209,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -3226,22 +3229,22 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3255,33 +3258,33 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3295,50 +3298,50 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -3346,39 +3349,39 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -3386,39 +3389,39 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -3426,19 +3429,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -3446,19 +3449,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -3466,19 +3469,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -3486,19 +3489,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -3506,19 +3509,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -3526,79 +3529,79 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -3606,19 +3609,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -3626,22 +3629,22 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3655,10 +3658,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3675,30 +3678,30 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3706,19 +3709,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3735,10 +3738,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3755,13 +3758,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3775,10 +3778,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3786,19 +3789,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="E71" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3806,22 +3809,22 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3835,10 +3838,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3855,13 +3858,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3875,90 +3878,90 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3975,13 +3978,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3995,10 +3998,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -4006,19 +4009,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="E82" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -4026,19 +4029,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -4046,19 +4049,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -4066,19 +4069,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -4086,19 +4089,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -4106,202 +4109,202 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="C90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>15</v>
+        <v>202</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>197</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>197</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>15</v>
+        <v>202</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>15</v>
+        <v>202</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4315,13 +4318,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -4335,13 +4338,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4355,33 +4358,33 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4395,13 +4398,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -4415,13 +4418,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4435,53 +4438,53 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4495,13 +4498,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4515,73 +4518,73 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4595,13 +4598,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4615,150 +4618,150 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>259</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>18</v>
+        <v>262</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -4766,19 +4769,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4786,122 +4789,122 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>147</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4915,10 +4918,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4926,19 +4929,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4946,19 +4949,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4966,19 +4969,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4986,19 +4989,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -5006,19 +5009,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -5026,19 +5029,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -5046,22 +5049,22 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5075,73 +5078,73 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>306</v>
+        <v>53</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -5155,93 +5158,93 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5255,10 +5258,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -5266,22 +5269,22 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>322</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5295,90 +5298,90 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F147" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -5386,22 +5389,22 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5415,90 +5418,90 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E153" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -5506,242 +5509,242 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>353</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>306</v>
+        <v>356</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>18</v>
+        <v>309</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5755,70 +5758,70 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5826,19 +5829,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5846,19 +5849,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5866,19 +5869,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5895,10 +5898,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5915,10 +5918,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5926,19 +5929,19 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5946,79 +5949,79 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -6035,13 +6038,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6055,10 +6058,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -6066,19 +6069,19 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -6086,19 +6089,19 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -6106,82 +6109,82 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6195,13 +6198,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6215,93 +6218,93 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>259</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="E193" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>51</v>
+        <v>262</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6315,13 +6318,13 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6335,13 +6338,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6355,73 +6358,73 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6435,173 +6438,173 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="E204" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>353</v>
+        <v>105</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>322</v>
+        <v>356</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>18</v>
+        <v>325</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6615,133 +6618,133 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="E213" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>306</v>
+        <v>79</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>5</v>
+        <v>309</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>479</v>
+        <v>53</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6755,53 +6758,53 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>322</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>479</v>
+        <v>325</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>4</v>
+        <v>147</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>322</v>
+        <v>482</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6815,470 +6818,470 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D223" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>486</v>
-      </c>
       <c r="E223" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>353</v>
+        <v>325</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>306</v>
+        <v>356</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>353</v>
+        <v>309</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>322</v>
+        <v>356</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>100</v>
+        <v>325</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>517</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7286,19 +7289,19 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>5</v>
@@ -7306,19 +7309,19 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>5</v>
@@ -7326,199 +7329,199 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>552</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>5</v>
@@ -7526,156 +7529,156 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>4</v>
@@ -7686,16 +7689,16 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D266" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="C266" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D266" s="1" t="s">
-        <v>577</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>8</v>
@@ -7706,139 +7709,139 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>5</v>
@@ -7846,19 +7849,19 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>5</v>
@@ -7866,19 +7869,19 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>5</v>
@@ -7886,199 +7889,199 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D279" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="B279" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="C279" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>604</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>5</v>
@@ -8086,59 +8089,59 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>5</v>
@@ -8146,19 +8149,19 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>5</v>
@@ -8166,96 +8169,96 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>633</v>
-      </c>
-      <c r="B292" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="C292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>632</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>14</v>
@@ -8266,99 +8269,99 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>5</v>
@@ -8366,19 +8369,19 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
@@ -8386,19 +8389,19 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>5</v>
@@ -8406,19 +8409,19 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>5</v>
@@ -8426,22 +8429,22 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
